--- a/가톨릭관동대학교-25학년도-정시.xlsx
+++ b/가톨릭관동대학교-25학년도-정시.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\findmyuniv data\findmyuniv_data_cleaning\"/>
@@ -26,14 +26,14 @@
     <sheet name="가톨릭관동대학교-25학년도-정시" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'가톨릭관동대학교-25학년도-정시'!$A$1:$DI$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'가톨릭관동대학교-25학년도-정시'!$A$1:$DI$78</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="429">
   <si>
     <t>비교대학 추가</t>
   </si>
@@ -1419,7 +1419,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1765,6 +1765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1786,6 +1787,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -3480,6 +3482,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -3851,7 +3854,8 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DC33"/>
+  <sheetPr codeName="Sheet12"/>
+  <dimension ref="A1:DC32"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.3984375" bestFit="1" customWidth="1"/>
@@ -4263,22 +4267,22 @@
         <v>5</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>316</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>317</v>
+        <v>223</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>318</v>
+        <v>224</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>319</v>
+        <v>225</v>
       </c>
       <c r="K2" s="4">
         <v>1000</v>
@@ -4286,35 +4290,37 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+        <v>175</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="R2" s="4" t="s">
         <v>129</v>
       </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4" t="s">
-        <v>149</v>
+        <v>227</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>148</v>
+        <v>228</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>191</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
@@ -4322,22 +4328,24 @@
         <v>426</v>
       </c>
       <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
+      <c r="AE2" s="4">
+        <v>20</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>30</v>
+      </c>
       <c r="AG2" s="4">
+        <v>30</v>
+      </c>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4">
         <v>20</v>
       </c>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
       <c r="AL2" s="4"/>
-      <c r="AM2" s="4">
-        <v>40</v>
-      </c>
-      <c r="AN2" s="4">
-        <v>40</v>
-      </c>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
       <c r="AO2" s="4"/>
       <c r="AP2" s="4"/>
       <c r="AQ2" s="4"/>
@@ -4361,31 +4369,31 @@
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
       <c r="BK2" s="4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="BL2" s="4">
-        <v>192.5</v>
+        <v>288.75</v>
       </c>
       <c r="BM2" s="4">
-        <v>185</v>
+        <v>277.5</v>
       </c>
       <c r="BN2" s="4">
-        <v>177.5</v>
+        <v>266.25</v>
       </c>
       <c r="BO2" s="4">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="BP2" s="4">
-        <v>162.5</v>
+        <v>243.75</v>
       </c>
       <c r="BQ2" s="4">
-        <v>155</v>
+        <v>232.5</v>
       </c>
       <c r="BR2" s="4">
-        <v>147.5</v>
+        <v>221.25</v>
       </c>
       <c r="BS2" s="4">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="BT2" s="4">
         <v>10</v>
@@ -4400,16 +4408,16 @@
         <v>10</v>
       </c>
       <c r="BX2" s="4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BY2" s="4">
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="BZ2" s="4">
-        <v>9</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="CA2" s="4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" s="4">
         <v>8</v>
@@ -4423,13 +4431,17 @@
       <c r="CI2" s="4"/>
       <c r="CJ2" s="4"/>
       <c r="CK2" s="4"/>
-      <c r="CL2" s="4"/>
+      <c r="CL2" s="4" t="s">
+        <v>427</v>
+      </c>
       <c r="CM2" s="4"/>
       <c r="CN2" s="4"/>
       <c r="CO2" s="4"/>
       <c r="CP2" s="4"/>
       <c r="CQ2" s="4"/>
-      <c r="CR2" s="4"/>
+      <c r="CR2" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CS2" s="4"/>
       <c r="CT2" s="4"/>
       <c r="CU2" s="4"/>
@@ -4450,64 +4462,60 @@
         <v>424</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="K3" s="4">
         <v>1000</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="4" t="s">
-        <v>130</v>
-      </c>
+      <c r="N3" s="4"/>
       <c r="O3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="P3" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>228</v>
-      </c>
       <c r="V3" s="4" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
@@ -4517,24 +4525,22 @@
         <v>426</v>
       </c>
       <c r="AD3" s="4"/>
-      <c r="AE3" s="4">
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4">
         <v>20</v>
       </c>
-      <c r="AF3" s="4">
-        <v>30</v>
-      </c>
-      <c r="AG3" s="4">
-        <v>30</v>
-      </c>
       <c r="AH3" s="4"/>
-      <c r="AI3" s="4">
-        <v>20</v>
-      </c>
+      <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
-      <c r="AM3" s="4"/>
-      <c r="AN3" s="4"/>
+      <c r="AM3" s="4">
+        <v>40</v>
+      </c>
+      <c r="AN3" s="4">
+        <v>40</v>
+      </c>
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
@@ -4558,31 +4564,31 @@
       <c r="BI3" s="4"/>
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="BL3" s="4">
-        <v>288.75</v>
+        <v>192.5</v>
       </c>
       <c r="BM3" s="4">
-        <v>277.5</v>
+        <v>185</v>
       </c>
       <c r="BN3" s="4">
-        <v>266.25</v>
+        <v>177.5</v>
       </c>
       <c r="BO3" s="4">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="BP3" s="4">
-        <v>243.75</v>
+        <v>162.5</v>
       </c>
       <c r="BQ3" s="4">
-        <v>232.5</v>
+        <v>155</v>
       </c>
       <c r="BR3" s="4">
-        <v>221.25</v>
+        <v>147.5</v>
       </c>
       <c r="BS3" s="4">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="BT3" s="4">
         <v>10</v>
@@ -4597,16 +4603,16 @@
         <v>10</v>
       </c>
       <c r="BX3" s="4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BY3" s="4">
-        <v>9.1999999999999993</v>
+        <v>9</v>
       </c>
       <c r="BZ3" s="4">
-        <v>8.8000000000000007</v>
+        <v>9</v>
       </c>
       <c r="CA3" s="4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB3" s="4">
         <v>8</v>
@@ -4620,17 +4626,13 @@
       <c r="CI3" s="4"/>
       <c r="CJ3" s="4"/>
       <c r="CK3" s="4"/>
-      <c r="CL3" s="4" t="s">
-        <v>427</v>
-      </c>
+      <c r="CL3" s="4"/>
       <c r="CM3" s="4"/>
       <c r="CN3" s="4"/>
       <c r="CO3" s="4"/>
       <c r="CP3" s="4"/>
       <c r="CQ3" s="4"/>
-      <c r="CR3" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CR3" s="4"/>
       <c r="CS3" s="4"/>
       <c r="CT3" s="4"/>
       <c r="CU3" s="4"/>
@@ -4651,62 +4653,62 @@
         <v>424</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>169</v>
+        <v>304</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>172</v>
+        <v>305</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="K4" s="4">
         <v>1000</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="N4" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="O4" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>164</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
       <c r="R4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>176</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
       <c r="W4" s="4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y4" s="4"/>
+        <v>238</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>257</v>
+      </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
@@ -4836,34 +4838,34 @@
     </row>
     <row r="5" spans="1:107" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>5</v>
+        <v>421</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>304</v>
+        <v>106</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="K5" s="4">
         <v>1000</v>
@@ -4871,33 +4873,31 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+        <v>116</v>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="W5" s="4" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>257</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
@@ -5027,34 +5027,34 @@
     </row>
     <row r="6" spans="1:107" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>421</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>106</v>
+        <v>284</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>108</v>
+        <v>229</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>109</v>
+        <v>285</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>111</v>
+        <v>286</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="K6" s="4">
         <v>1000</v>
@@ -5062,29 +5062,31 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+        <v>288</v>
+      </c>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="R6" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="V6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="W6" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="W6" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="X6" s="4" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
@@ -5228,22 +5230,22 @@
         <v>5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>229</v>
+        <v>161</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K7" s="4">
         <v>1000</v>
@@ -5251,31 +5253,29 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>119</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
       <c r="R7" s="4" t="s">
         <v>120</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
@@ -5419,52 +5419,52 @@
         <v>5</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>292</v>
+        <v>247</v>
       </c>
       <c r="K8" s="4">
         <v>1000</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="4" t="s">
-        <v>147</v>
-      </c>
+      <c r="N8" s="4"/>
       <c r="O8" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+        <v>226</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>242</v>
+      </c>
       <c r="R8" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="T8" s="4" t="s">
+        <v>235</v>
+      </c>
       <c r="U8" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>186</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
       <c r="X8" s="4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
@@ -5602,56 +5602,58 @@
         <v>424</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>244</v>
+        <v>179</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="K9" s="4">
         <v>1000</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4" t="s">
-        <v>226</v>
-      </c>
+      <c r="N9" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="O9" s="4"/>
       <c r="P9" s="4" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>242</v>
+        <v>184</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="S9" s="4"/>
       <c r="T9" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
+        <v>159</v>
+      </c>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="X9" s="4" t="s">
         <v>129</v>
       </c>
@@ -5797,22 +5799,22 @@
         <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="K10" s="4">
         <v>1000</v>
@@ -5820,31 +5822,31 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="S10" s="4"/>
       <c r="T10" s="4" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
@@ -5982,60 +5984,60 @@
         <v>424</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>132</v>
+        <v>267</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>135</v>
+        <v>269</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c r="K11" s="4">
         <v>1000</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="O11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="P11" s="4" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>129</v>
       </c>
       <c r="S11" s="4"/>
-      <c r="T11" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="U11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="V11" s="4" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>139</v>
+        <v>271</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
@@ -6173,61 +6175,61 @@
         <v>424</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>268</v>
+        <v>195</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>269</v>
+        <v>196</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="K12" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4" t="s">
+        <v>164</v>
+      </c>
       <c r="O12" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="W12" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="P12" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -6275,31 +6277,31 @@
       <c r="BI12" s="4"/>
       <c r="BJ12" s="4"/>
       <c r="BK12" s="4">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="BL12" s="4">
-        <v>192.5</v>
+        <v>115.5</v>
       </c>
       <c r="BM12" s="4">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="BN12" s="4">
-        <v>177.5</v>
+        <v>106.5</v>
       </c>
       <c r="BO12" s="4">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="BP12" s="4">
-        <v>162.5</v>
+        <v>97.5</v>
       </c>
       <c r="BQ12" s="4">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="BR12" s="4">
-        <v>147.5</v>
+        <v>88.5</v>
       </c>
       <c r="BS12" s="4">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="BT12" s="4">
         <v>10</v>
@@ -6370,22 +6372,22 @@
         <v>5</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>143</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="K13" s="4">
         <v>600</v>
@@ -6393,30 +6395,28 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>199</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O13" s="4"/>
       <c r="P13" s="4" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
@@ -6555,60 +6555,64 @@
         <v>424</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>202</v>
+        <v>313</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>204</v>
+        <v>315</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>205</v>
+        <v>315</v>
       </c>
       <c r="K14" s="4">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="O14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="P14" s="4" t="s">
-        <v>139</v>
+        <v>238</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="R14" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>170</v>
+      </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
+      <c r="Y14" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
       <c r="AB14" s="4"/>
@@ -6655,31 +6659,31 @@
       <c r="BI14" s="4"/>
       <c r="BJ14" s="4"/>
       <c r="BK14" s="4">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="BL14" s="4">
-        <v>115.5</v>
+        <v>192.5</v>
       </c>
       <c r="BM14" s="4">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="BN14" s="4">
-        <v>106.5</v>
+        <v>177.5</v>
       </c>
       <c r="BO14" s="4">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="BP14" s="4">
-        <v>97.5</v>
+        <v>162.5</v>
       </c>
       <c r="BQ14" s="4">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="BR14" s="4">
-        <v>88.5</v>
+        <v>147.5</v>
       </c>
       <c r="BS14" s="4">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="BT14" s="4">
         <v>10</v>
@@ -6750,58 +6754,56 @@
         <v>5</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="K15" s="4">
         <v>1000</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="N15" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="O15" s="4"/>
       <c r="P15" s="4" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="U15" s="4" t="s">
-        <v>238</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="U15" s="4"/>
       <c r="V15" s="4" t="s">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4" t="s">
-        <v>141</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
@@ -6943,22 +6945,22 @@
         <v>5</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K16" s="4">
         <v>1000</v>
@@ -6966,28 +6968,28 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="Q16" s="4" t="s">
         <v>242</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="S16" s="4"/>
-      <c r="T16" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="U16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4" t="s">
+        <v>164</v>
+      </c>
       <c r="V16" s="4" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="X16" s="4" t="s">
         <v>129</v>
@@ -7134,22 +7136,22 @@
         <v>5</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>259</v>
+        <v>151</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>260</v>
+        <v>116</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="K17" s="4">
         <v>1000</v>
@@ -7157,29 +7159,25 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>242</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
       <c r="R17" s="4" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
+      <c r="T17" s="4" t="s">
+        <v>186</v>
+      </c>
       <c r="U17" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="W17" s="4" t="s">
-        <v>234</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
       <c r="X17" s="4" t="s">
         <v>129</v>
       </c>
@@ -7325,22 +7323,22 @@
         <v>5</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>143</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>151</v>
+        <v>300</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>116</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
       <c r="K18" s="4">
         <v>1000</v>
@@ -7348,29 +7346,35 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
+        <v>288</v>
+      </c>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="R18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="U18" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
       <c r="X18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y18" s="4"/>
+        <v>121</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>165</v>
+      </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
@@ -7512,22 +7516,22 @@
         <v>5</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>299</v>
+        <v>45</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>301</v>
+        <v>215</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>302</v>
+        <v>216</v>
       </c>
       <c r="K19" s="4">
         <v>1000</v>
@@ -7535,58 +7539,64 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="O19" s="4"/>
+        <v>217</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>218</v>
+      </c>
       <c r="P19" s="4" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>303</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="S19" s="4"/>
       <c r="T19" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
+        <v>220</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>221</v>
+      </c>
       <c r="W19" s="4" t="s">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y19" s="4" t="s">
-        <v>165</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
+      <c r="AB19" s="4" t="s">
+        <v>428</v>
+      </c>
       <c r="AC19" s="4" t="s">
         <v>426</v>
       </c>
       <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
+      <c r="AE19" s="4">
+        <v>20</v>
+      </c>
+      <c r="AF19" s="4">
+        <v>30</v>
+      </c>
       <c r="AG19" s="4">
         <v>20</v>
       </c>
       <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
+      <c r="AI19" s="4">
+        <v>30</v>
+      </c>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
-      <c r="AM19" s="4">
-        <v>40</v>
-      </c>
-      <c r="AN19" s="4">
-        <v>40</v>
-      </c>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="4"/>
       <c r="AO19" s="4"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
@@ -7672,13 +7682,17 @@
       <c r="CI19" s="4"/>
       <c r="CJ19" s="4"/>
       <c r="CK19" s="4"/>
-      <c r="CL19" s="4"/>
+      <c r="CL19" s="4" t="s">
+        <v>427</v>
+      </c>
       <c r="CM19" s="4"/>
       <c r="CN19" s="4"/>
       <c r="CO19" s="4"/>
       <c r="CP19" s="4"/>
       <c r="CQ19" s="4"/>
-      <c r="CR19" s="4"/>
+      <c r="CR19" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CS19" s="4"/>
       <c r="CT19" s="4"/>
       <c r="CU19" s="4"/>
@@ -7705,22 +7719,22 @@
         <v>5</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>45</v>
+        <v>230</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="K20" s="4">
         <v>1000</v>
@@ -7728,64 +7742,54 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>219</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
       <c r="R20" s="4" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="S20" s="4"/>
       <c r="T20" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>219</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="U20" s="4"/>
       <c r="V20" s="4" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
-      <c r="AB20" s="4" t="s">
-        <v>428</v>
-      </c>
+      <c r="AB20" s="4"/>
       <c r="AC20" s="4" t="s">
         <v>426</v>
       </c>
       <c r="AD20" s="4"/>
-      <c r="AE20" s="4">
-        <v>20</v>
-      </c>
-      <c r="AF20" s="4">
-        <v>30</v>
-      </c>
+      <c r="AE20" s="4"/>
+      <c r="AF20" s="4"/>
       <c r="AG20" s="4">
         <v>20</v>
       </c>
       <c r="AH20" s="4"/>
-      <c r="AI20" s="4">
-        <v>30</v>
-      </c>
+      <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
-      <c r="AM20" s="4"/>
-      <c r="AN20" s="4"/>
+      <c r="AM20" s="4">
+        <v>40</v>
+      </c>
+      <c r="AN20" s="4">
+        <v>40</v>
+      </c>
       <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
@@ -7871,17 +7875,13 @@
       <c r="CI20" s="4"/>
       <c r="CJ20" s="4"/>
       <c r="CK20" s="4"/>
-      <c r="CL20" s="4" t="s">
-        <v>427</v>
-      </c>
+      <c r="CL20" s="4"/>
       <c r="CM20" s="4"/>
       <c r="CN20" s="4"/>
       <c r="CO20" s="4"/>
       <c r="CP20" s="4"/>
       <c r="CQ20" s="4"/>
-      <c r="CR20" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CR20" s="4"/>
       <c r="CS20" s="4"/>
       <c r="CT20" s="4"/>
       <c r="CU20" s="4"/>
@@ -7908,22 +7908,22 @@
         <v>5</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="K21" s="4">
         <v>1000</v>
@@ -7931,29 +7931,27 @@
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4" t="s">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="S21" s="4"/>
       <c r="T21" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="W21" s="4" t="s">
-        <v>234</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
       <c r="X21" s="4" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
@@ -8091,54 +8089,58 @@
         <v>424</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>279</v>
+        <v>150</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>280</v>
+        <v>151</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>281</v>
+        <v>152</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>282</v>
+        <v>153</v>
       </c>
       <c r="K22" s="4">
         <v>1000</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="N22" s="4"/>
       <c r="O22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="P22" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="R22" s="4" t="s">
         <v>140</v>
       </c>
       <c r="S22" s="4"/>
-      <c r="T22" s="4" t="s">
-        <v>283</v>
-      </c>
+      <c r="T22" s="4"/>
       <c r="U22" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="X22" s="4" t="s">
         <v>120</v>
       </c>
@@ -8278,60 +8280,60 @@
         <v>424</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>151</v>
+        <v>249</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>152</v>
+        <v>250</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>153</v>
+        <v>251</v>
       </c>
       <c r="K23" s="4">
         <v>1000</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="N23" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O23" s="4"/>
       <c r="P23" s="4" t="s">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>131</v>
+        <v>253</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4" t="s">
-        <v>155</v>
-      </c>
+      <c r="T23" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="U23" s="4"/>
       <c r="V23" s="4" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
@@ -8475,55 +8477,53 @@
         <v>5</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>249</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="K24" s="4">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>118</v>
+        <v>235</v>
       </c>
       <c r="O24" s="4"/>
       <c r="P24" s="4" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="U24" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>168</v>
+      </c>
       <c r="V24" s="4" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
@@ -8571,31 +8571,31 @@
       <c r="BI24" s="4"/>
       <c r="BJ24" s="4"/>
       <c r="BK24" s="4">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="BL24" s="4">
-        <v>192.5</v>
+        <v>134.75</v>
       </c>
       <c r="BM24" s="4">
-        <v>185</v>
+        <v>129.5</v>
       </c>
       <c r="BN24" s="4">
-        <v>177.5</v>
+        <v>124.25</v>
       </c>
       <c r="BO24" s="4">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="BP24" s="4">
-        <v>162.5</v>
+        <v>113.75</v>
       </c>
       <c r="BQ24" s="4">
-        <v>155</v>
+        <v>108.5</v>
       </c>
       <c r="BR24" s="4">
-        <v>147.5</v>
+        <v>103.25</v>
       </c>
       <c r="BS24" s="4">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="BT24" s="4">
         <v>10</v>
@@ -8666,53 +8666,55 @@
         <v>5</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>33</v>
+        <v>236</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>260</v>
+        <v>116</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="K25" s="4">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="O25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4" t="s">
+        <v>200</v>
+      </c>
       <c r="P25" s="4" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="R25" s="4"/>
+        <v>241</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>166</v>
+      </c>
       <c r="S25" s="4"/>
-      <c r="T25" s="4" t="s">
-        <v>147</v>
-      </c>
+      <c r="T25" s="4"/>
       <c r="U25" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="X25" s="4"/>
+        <v>242</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
@@ -8760,31 +8762,31 @@
       <c r="BI25" s="4"/>
       <c r="BJ25" s="4"/>
       <c r="BK25" s="4">
+        <v>200</v>
+      </c>
+      <c r="BL25" s="4">
+        <v>192.5</v>
+      </c>
+      <c r="BM25" s="4">
+        <v>185</v>
+      </c>
+      <c r="BN25" s="4">
+        <v>177.5</v>
+      </c>
+      <c r="BO25" s="4">
+        <v>170</v>
+      </c>
+      <c r="BP25" s="4">
+        <v>162.5</v>
+      </c>
+      <c r="BQ25" s="4">
+        <v>155</v>
+      </c>
+      <c r="BR25" s="4">
+        <v>147.5</v>
+      </c>
+      <c r="BS25" s="4">
         <v>140</v>
-      </c>
-      <c r="BL25" s="4">
-        <v>134.75</v>
-      </c>
-      <c r="BM25" s="4">
-        <v>129.5</v>
-      </c>
-      <c r="BN25" s="4">
-        <v>124.25</v>
-      </c>
-      <c r="BO25" s="4">
-        <v>119</v>
-      </c>
-      <c r="BP25" s="4">
-        <v>113.75</v>
-      </c>
-      <c r="BQ25" s="4">
-        <v>108.5</v>
-      </c>
-      <c r="BR25" s="4">
-        <v>103.25</v>
-      </c>
-      <c r="BS25" s="4">
-        <v>98</v>
       </c>
       <c r="BT25" s="4">
         <v>10</v>
@@ -8855,22 +8857,22 @@
         <v>5</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>237</v>
+        <v>129</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="K26" s="4">
         <v>1000</v>
@@ -8879,24 +8881,24 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>208</v>
+        <v>148</v>
       </c>
       <c r="Q26" s="4" t="s">
         <v>241</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="W26" s="4" t="s">
         <v>242</v>
@@ -9046,22 +9048,22 @@
         <v>5</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="F27" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>245</v>
-      </c>
       <c r="I27" s="4" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="K27" s="4">
         <v>1000</v>
@@ -9070,32 +9072,36 @@
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="R27" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="V27" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="W27" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="V27" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="W27" s="4" t="s">
-        <v>242</v>
-      </c>
       <c r="X27" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y27" s="4"/>
+        <v>130</v>
+      </c>
+      <c r="Y27" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
       <c r="AB27" s="4"/>
@@ -9231,66 +9237,58 @@
         <v>424</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>296</v>
+        <v>151</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>297</v>
+        <v>162</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>298</v>
+        <v>163</v>
       </c>
       <c r="K28" s="4">
         <v>1000</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+      <c r="N28" s="4" t="s">
+        <v>164</v>
+      </c>
       <c r="O28" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q28" s="4" t="s">
-        <v>138</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
       <c r="R28" s="4" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="S28" s="4"/>
       <c r="T28" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="U28" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="U28" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="V28" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="W28" s="4" t="s">
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="X28" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y28" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
       <c r="AB28" s="4"/>
@@ -9426,28 +9424,28 @@
         <v>424</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>160</v>
+        <v>307</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>151</v>
+        <v>308</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>129</v>
+        <v>309</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>162</v>
+        <v>310</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>163</v>
+        <v>311</v>
       </c>
       <c r="K29" s="4">
         <v>1000</v>
@@ -9455,29 +9453,37 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
+        <v>312</v>
+      </c>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>200</v>
+      </c>
       <c r="R29" s="4" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="S29" s="4"/>
       <c r="T29" s="4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
+        <v>184</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="X29" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y29" s="4"/>
+        <v>191</v>
+      </c>
+      <c r="Y29" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
       <c r="AB29" s="4"/>
@@ -9613,28 +9619,28 @@
         <v>424</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>308</v>
+        <v>188</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>309</v>
+        <v>123</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>310</v>
+        <v>189</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="K30" s="4">
         <v>1000</v>
@@ -9642,37 +9648,29 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
       <c r="R30" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="S30" s="4"/>
       <c r="T30" s="4" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="V30" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="W30" s="4" t="s">
-        <v>120</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
       <c r="X30" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y30" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
       <c r="AB30" s="4"/>
@@ -9814,22 +9812,22 @@
         <v>5</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>123</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="K31" s="4">
         <v>1000</v>
@@ -9837,10 +9835,10 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
@@ -9849,10 +9847,10 @@
       </c>
       <c r="S31" s="4"/>
       <c r="T31" s="4" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
@@ -10001,50 +9999,54 @@
         <v>5</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="K32" s="4">
         <v>1000</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
-      <c r="N32" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="N32" s="4"/>
       <c r="O32" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="R32" s="4" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="S32" s="4"/>
-      <c r="T32" s="4" t="s">
-        <v>118</v>
-      </c>
+      <c r="T32" s="4"/>
       <c r="U32" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
+        <v>147</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="X32" s="4" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
@@ -10174,197 +10176,6 @@
       <c r="DB32" s="4"/>
       <c r="DC32" s="4"/>
     </row>
-    <row r="33" spans="1:107" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="K33" s="4">
-        <v>1000</v>
-      </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q33" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="R33" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="V33" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="W33" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="X33" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="AD33" s="4"/>
-      <c r="AE33" s="4"/>
-      <c r="AF33" s="4"/>
-      <c r="AG33" s="4">
-        <v>20</v>
-      </c>
-      <c r="AH33" s="4"/>
-      <c r="AI33" s="4"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="4"/>
-      <c r="AL33" s="4"/>
-      <c r="AM33" s="4">
-        <v>40</v>
-      </c>
-      <c r="AN33" s="4">
-        <v>40</v>
-      </c>
-      <c r="AO33" s="4"/>
-      <c r="AP33" s="4"/>
-      <c r="AQ33" s="4"/>
-      <c r="AR33" s="4"/>
-      <c r="AS33" s="4"/>
-      <c r="AT33" s="4"/>
-      <c r="AU33" s="4"/>
-      <c r="AV33" s="4"/>
-      <c r="AW33" s="4"/>
-      <c r="AX33" s="4"/>
-      <c r="AY33" s="4"/>
-      <c r="AZ33" s="4"/>
-      <c r="BA33" s="4"/>
-      <c r="BB33" s="4"/>
-      <c r="BC33" s="4"/>
-      <c r="BD33" s="4"/>
-      <c r="BE33" s="4"/>
-      <c r="BF33" s="4"/>
-      <c r="BG33" s="4"/>
-      <c r="BH33" s="4"/>
-      <c r="BI33" s="4"/>
-      <c r="BJ33" s="4"/>
-      <c r="BK33" s="4">
-        <v>200</v>
-      </c>
-      <c r="BL33" s="4">
-        <v>192.5</v>
-      </c>
-      <c r="BM33" s="4">
-        <v>185</v>
-      </c>
-      <c r="BN33" s="4">
-        <v>177.5</v>
-      </c>
-      <c r="BO33" s="4">
-        <v>170</v>
-      </c>
-      <c r="BP33" s="4">
-        <v>162.5</v>
-      </c>
-      <c r="BQ33" s="4">
-        <v>155</v>
-      </c>
-      <c r="BR33" s="4">
-        <v>147.5</v>
-      </c>
-      <c r="BS33" s="4">
-        <v>140</v>
-      </c>
-      <c r="BT33" s="4">
-        <v>10</v>
-      </c>
-      <c r="BU33" s="4">
-        <v>10</v>
-      </c>
-      <c r="BV33" s="4">
-        <v>10</v>
-      </c>
-      <c r="BW33" s="4">
-        <v>10</v>
-      </c>
-      <c r="BX33" s="4">
-        <v>9</v>
-      </c>
-      <c r="BY33" s="4">
-        <v>9</v>
-      </c>
-      <c r="BZ33" s="4">
-        <v>9</v>
-      </c>
-      <c r="CA33" s="4">
-        <v>8</v>
-      </c>
-      <c r="CB33" s="4">
-        <v>8</v>
-      </c>
-      <c r="CC33" s="4"/>
-      <c r="CD33" s="4"/>
-      <c r="CE33" s="4"/>
-      <c r="CF33" s="4"/>
-      <c r="CG33" s="4"/>
-      <c r="CH33" s="4"/>
-      <c r="CI33" s="4"/>
-      <c r="CJ33" s="4"/>
-      <c r="CK33" s="4"/>
-      <c r="CL33" s="4"/>
-      <c r="CM33" s="4"/>
-      <c r="CN33" s="4"/>
-      <c r="CO33" s="4"/>
-      <c r="CP33" s="4"/>
-      <c r="CQ33" s="4"/>
-      <c r="CR33" s="4"/>
-      <c r="CS33" s="4"/>
-      <c r="CT33" s="4"/>
-      <c r="CU33" s="4"/>
-      <c r="CV33" s="4"/>
-      <c r="CW33" s="4"/>
-      <c r="CX33" s="4"/>
-      <c r="CY33" s="4"/>
-      <c r="CZ33" s="4"/>
-      <c r="DA33" s="4"/>
-      <c r="DB33" s="4"/>
-      <c r="DC33" s="4"/>
-    </row>
   </sheetData>
   <sortState ref="A2:DI33">
     <sortCondition ref="E2:E33"/>
@@ -10377,6 +10188,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -10396,6 +10208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -10444,6 +10257,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -10570,6 +10384,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -10669,6 +10484,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -10730,6 +10546,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -10781,6 +10598,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -10800,6 +10618,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
